--- a/mst-qms/원본_정정본/9_정정내역_및_연동표/원본대비_정정내역.xlsx
+++ b/mst-qms/원본_정정본/9_정정내역_및_연동표/원본대비_정정내역.xlsx
@@ -41098,7 +41098,7 @@
       </c>
       <c r="E1760" s="4" t="inlineStr">
         <is>
-          <t>ㅡ 대표이사  : 김맹권</t>
+          <t>ㅡ 대표이사  : 김명권</t>
         </is>
       </c>
     </row>
